--- a/Reporte de Bugs/Reporte de  Bugs_Test Cases -v 3.0.xlsx
+++ b/Reporte de Bugs/Reporte de  Bugs_Test Cases -v 3.0.xlsx
@@ -5,9 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Curso de Marllulit\Curso QA\Plantillas de Pruebas\Plantilla_Bug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Portafolio\Reporte de Bugs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="YaMkLCQSzmvby0vq6IQXsbXp6wqRB1cANo2jLjmUL1R+9+okKZ+VYSUVUhDMFM5QwJy6Lr8GyQ92dqRyrWkCgA==" workbookSaltValue="fLpDjxUK9B1Yec5+7fvOmQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="3"/>
   </bookViews>
@@ -186,9 +187,6 @@
     <t>1.2 Alcance</t>
   </si>
   <si>
-    <t>Incluye: Autenticación, Dashboard, Transferencias.</t>
-  </si>
-  <si>
     <t>Bug-CP-08</t>
   </si>
   <si>
@@ -255,6 +253,9 @@
   </si>
   <si>
     <t>Cierre de sesión y borrado de historial tras error de validación (F5) /(Pérdida de datos).</t>
+  </si>
+  <si>
+    <t>Incluye: Autenticación, Dashboard, Transferencias.</t>
   </si>
 </sst>
 </file>
@@ -643,135 +644,135 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1216,142 +1217,143 @@
       <c r="D1" s="35"/>
       <c r="E1" s="35"/>
       <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
     </row>
     <row r="11" spans="1:7" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
     </row>
     <row r="13" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
+      <c r="A14" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="ylqGyHaBh2EzMOavJCoymW7RiuIMgNlHQLjejzh7rxsXZxPdgbvYMzdCRBD2DxBaBAeHfC5MyCoyAr7ndt1Cmg==" saltValue="MuBchRbhB5F1quota9wVZg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -1371,17 +1373,17 @@
   <dimension ref="B1:T41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="5" customWidth="1"/>
-    <col min="2" max="3" width="55.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="3.42578125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="55.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:20" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
+      <c r="C1" s="41"/>
     </row>
     <row r="2" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -1392,130 +1394,130 @@
       </c>
     </row>
     <row r="3" spans="2:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>46087</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="25" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="T9" s="11"/>
+      <c r="M9" s="8"/>
+      <c r="T9" s="9"/>
     </row>
     <row r="10" spans="2:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="22" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="2:20" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="2:20" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="19" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:3" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" spans="2:3" ht="375" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="45"/>
     </row>
     <row r="22" spans="2:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -1524,10 +1526,10 @@
       </c>
     </row>
     <row r="24" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-    </row>
-    <row r="25" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -1536,10 +1538,10 @@
       </c>
     </row>
     <row r="26" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1557,6 +1559,7 @@
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="GoE79qhlOQmCMBkQXdBlm2w9fHzmhxHIAXMG18ckQso1wHxfuuLWlswd1hSpOlAzo1wyRwrBE4MS2srKy6RAHw==" saltValue="JwT2ywpIFu79Rpqp0uHr9g==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B20:C20"/>
@@ -1579,17 +1582,17 @@
   <dimension ref="B1:T41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="5" customWidth="1"/>
-    <col min="2" max="3" width="55.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="3.42578125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="55.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:20" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
+      <c r="C1" s="41"/>
     </row>
     <row r="2" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -1600,130 +1603,130 @@
       </c>
     </row>
     <row r="3" spans="2:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="8">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6">
         <v>46087</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="25" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="T9" s="9"/>
+    </row>
+    <row r="10" spans="2:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" s="10"/>
-      <c r="T9" s="11"/>
-    </row>
-    <row r="10" spans="2:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="30" t="s">
+    </row>
+    <row r="12" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="14" spans="2:20" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="2:20" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="2:20" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="19" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:3" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" spans="2:3" ht="375" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="45"/>
     </row>
     <row r="22" spans="2:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -1732,10 +1735,10 @@
       </c>
     </row>
     <row r="24" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-    </row>
-    <row r="25" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -1744,11 +1747,11 @@
       </c>
     </row>
     <row r="26" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>51</v>
+      <c r="C26" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1765,6 +1768,7 @@
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="0NkE9UzB4Vehgq28Ay8crrdS3V/Uk18b9xC1G6P5T/ddzEOh7tt0gokz2b61fClUBkHDcs4otvK+glDbd5McMQ==" saltValue="8ecAWaAGUfZ8Z+LdYH9YmA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B20:C20"/>
@@ -1786,17 +1790,17 @@
   <dimension ref="B1:T41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="5" customWidth="1"/>
-    <col min="2" max="3" width="55.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="3.42578125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="55.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:20" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
+      <c r="C1" s="41"/>
     </row>
     <row r="2" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -1807,130 +1811,130 @@
       </c>
     </row>
     <row r="3" spans="2:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="6">
         <v>46087</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="25" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="M9" s="8"/>
+      <c r="T9" s="9"/>
+    </row>
+    <row r="10" spans="2:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="T9" s="11"/>
-    </row>
-    <row r="10" spans="2:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="12" t="s">
+      <c r="C11" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="30" t="s">
+    </row>
+    <row r="12" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="14" spans="2:20" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="2:20" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="2:20" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="19" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:3" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" spans="2:3" ht="375" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="45"/>
     </row>
     <row r="22" spans="2:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -1939,10 +1943,10 @@
       </c>
     </row>
     <row r="24" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-    </row>
-    <row r="25" spans="2:3" s="4" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" spans="2:3" s="2" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -1951,11 +1955,11 @@
       </c>
     </row>
     <row r="26" spans="2:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>59</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1972,6 +1976,7 @@
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="GwV686n3lo2xXOGXsGbX3wtbfaiJL/4T7ZZ2qcGzDJU+3wJARLL6b1LyBy9j+zrhnQcBpVkbSpDEbFnZcxUhvw==" saltValue="z6AxXmSY12DGvKEN09rYbQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B20:C20"/>
